--- a/tests/fixtures/ratio_z1_2026-04-07.xlsx
+++ b/tests/fixtures/ratio_z1_2026-04-07.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ratio_value</t>
+          <t>value_ratio</t>
         </is>
       </c>
     </row>
